--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\DSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\DSA_PRACTICE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE95AA31-7F3E-4856-8B42-2F765253B948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34ADC86-E97B-45B4-8C50-37395AE23354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t>Given an array containing only 0, 1, and 2, sort the array in ascending order in place without using a sorting function</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>Given a sorted array of integers and a target value, find two distinct elements whose sum equals the target.</t>
+  </si>
+  <si>
+    <t>Reverse an array without creating another array.</t>
+  </si>
+  <si>
+    <t>Given an array height where each element represents the height of a vertical line, find two lines that, together with the x-axis, can contain the maximum amount of water.</t>
   </si>
 </sst>
 </file>
@@ -121,11 +127,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,10 +465,18 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -499,11 +516,19 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\DSA_PRACTICE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34ADC86-E97B-45B4-8C50-37395AE23354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B658A5A-DF0B-4D93-986B-7F9342336FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>Given an array containing only 0, 1, and 2, sort the array in ascending order in place without using a sorting function</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Optimal sol (2-pointer)</t>
   </si>
   <si>
-    <t>Given a sorted array of integers, return a new array containing the squares of every number, also sorted in ascending order</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
@@ -62,13 +59,31 @@
   </si>
   <si>
     <t>Given an array height where each element represents the height of a vertical line, find two lines that, together with the x-axis, can contain the maximum amount of water.</t>
+  </si>
+  <si>
+    <t>Given a sorted integer array, remove duplicates in place so that each distinct element appears at most twice</t>
+  </si>
+  <si>
+    <t>Given an integer array, move all negative numbers to the beginning and all non-negative numbers to the end. Maintain the relative order of elements within both groups.</t>
+  </si>
+  <si>
+    <t>Given an array and an integer k, remove all occurrences of k in place</t>
+  </si>
+  <si>
+    <t>Given a sorted array of integers, return a new array containing the squares of every number, also sorted in ascending order.</t>
+  </si>
+  <si>
+    <t>Given an integer array, rearrange it so that all even numbers appear before all odd numbers.</t>
+  </si>
+  <si>
+    <t>Given two sorted arrays, merge them into a single sorted array</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +102,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -127,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -135,6 +156,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,33 +472,43 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
+      <c r="A2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
+      <c r="A5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>4</v>
       </c>
@@ -485,46 +520,62 @@
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\DSA_PRACTICE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B658A5A-DF0B-4D93-986B-7F9342336FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88ED95F-A12F-4A55-BC6F-181DA8F60770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="two-pointer" sheetId="2" r:id="rId2"/>
+    <sheet name="arr - single-pass traversal" sheetId="1" r:id="rId1"/>
+    <sheet name="arr - two-pointer" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="29">
   <si>
     <t>Given an array containing only 0, 1, and 2, sort the array in ascending order in place without using a sorting function</t>
   </si>
@@ -77,6 +77,46 @@
   </si>
   <si>
     <t>Given two sorted arrays, merge them into a single sorted array</t>
+  </si>
+  <si>
+    <t>Given an array of integers, count the number of even and odd numbers.</t>
+  </si>
+  <si>
+    <t>Given a binary array containing only 0 and 1, find the maximum number of consecutive ones.</t>
+  </si>
+  <si>
+    <t>Given an array where each element represents a stock price on a particular day, find the maximum profit possible from one purchase followed by one sale. You must buy before you sell. If no profit is possible, return 0.</t>
+  </si>
+  <si>
+    <t>Given an array of integers, find the maximum value of arr[j] - arr[i], where j &gt; i. The second element must appear after the first element in the array.</t>
+  </si>
+  <si>
+    <t>An array contains n distinct integers from the range 0 to n, with exactly one number missing. Find the missing number.</t>
+  </si>
+  <si>
+    <t>Given an array of integers, find the first repeating element. The first repeating element is the element whose first occurrence has the smallest index among all elements that appear more than once. If no element repeats, return -1</t>
+  </si>
+  <si>
+    <t>Given an array of integers, find the first index where the sum of all elements to the left equals the sum of all elements to the right. The element at the index itself is excluded from both sums. If no equilibrium index exists, return -1.</t>
+  </si>
+  <si>
+    <t>brute-force</t>
+  </si>
+  <si>
+    <t>single-pass approach</t>
+  </si>
+  <si>
+    <t>Problems</t>
+  </si>
+  <si>
+    <t>Given an array of integers, find the maximum sum of a non-empty contiguous subarray.
+Input: arr = [-2, 1, -3, 4, -1, 2, 1, -5, 4]
+Output: 6</t>
+  </si>
+  <si>
+    <t>Given an array of integers, find the element that appears more than n // 2 times, where n is the length of the array. If no such element exists, return -1.
+Input: arr = [2, 2, 1, 1, 2, 2, 2]
+Output: 2</t>
   </si>
 </sst>
 </file>
@@ -440,10 +480,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="110.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
